--- a/data/trans_bre/IP16B98-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP16B98-Habitat-trans_bre.xlsx
@@ -661,22 +661,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-18,06; 44,42</t>
+          <t>-18,03; 43,28</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,15</t>
+          <t>0,0; 36,37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-18,09; 89,13</t>
+          <t>-18,04; 76,44</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 67,07</t>
+          <t>0,0; 58,72</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 57,19</t>
+          <t>0,0; 57,75</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 133,59</t>
+          <t>0,0; 136,7</t>
         </is>
       </c>
     </row>
@@ -781,22 +781,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,16</t>
+          <t>0,0; 45,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-62,56; 0,0</t>
+          <t>-63,4; 0,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 82,35</t>
+          <t>0,0; 82,93</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-62,56; 0,0</t>
+          <t>-63,4; 0,0</t>
         </is>
       </c>
     </row>
@@ -841,22 +841,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-13,86; 16,2</t>
+          <t>-11,01; 16,41</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 17,21</t>
+          <t>-3,73; 16,81</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-14,33; 19,87</t>
+          <t>-11,43; 20,33</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 21,45</t>
+          <t>-4,01; 20,64</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16B98-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP16B98-Habitat-trans_bre.xlsx
@@ -661,22 +661,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-18,03; 43,28</t>
+          <t>-18,06; 44,12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,37</t>
+          <t>0,0; 40,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-18,04; 76,44</t>
+          <t>-18,07; 82,77</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 58,72</t>
+          <t>0,0; 68,09</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 57,75</t>
+          <t>0,0; 57,19</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 136,7</t>
+          <t>0,0; 133,61</t>
         </is>
       </c>
     </row>
@@ -781,22 +781,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,33</t>
+          <t>0,0; 45,54</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-63,4; 0,0</t>
+          <t>-61,42; 0,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 82,93</t>
+          <t>0,0; 83,62</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-63,4; 0,0</t>
+          <t>-61,42; 0,0</t>
         </is>
       </c>
     </row>
@@ -841,22 +841,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-11,01; 16,41</t>
+          <t>-12,83; 14,65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 16,81</t>
+          <t>-4,58; 16,76</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-11,43; 20,33</t>
+          <t>-13,96; 17,84</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 20,64</t>
+          <t>-4,7; 20,41</t>
         </is>
       </c>
     </row>
